--- a/data/export/2026-10-23-浦东78路.xlsx
+++ b/data/export/2026-10-23-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,36 +632,32 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -669,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,37 +689,33 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -895,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -945,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -953,22 +945,22 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1001,12 +993,12 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1020,7 +1012,7 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1056,7 +1048,1339 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东78路.xlsx
+++ b/data/export/2026-10-23-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -887,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -937,7 +953,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -965,32 +981,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -998,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1042,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1100,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1109,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,33 +1161,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1441,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1442,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1466,33 +1502,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1643,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1704,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1703,7 +1743,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1714,7 +1754,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1865,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1976,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2037,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2087,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2148,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2198,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2309,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2277,22 +2317,22 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>07:57</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2325,12 +2365,12 @@
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2344,7 +2384,7 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2369,7 +2409,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2380,7 +2420,1026 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东78路.xlsx
+++ b/data/export/2026-10-23-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -870,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -903,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -927,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -947,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1137,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1219,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1252,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1593,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,32 +1687,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -1704,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1728,17 +1748,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1748,13 +1768,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1926,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,7 +2061,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2148,7 +2172,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,7 +2283,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,7 +2394,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2505,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2620,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2707,7 +2731,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,7 +2846,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2937,7 +2961,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3048,7 +3072,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3163,7 +3187,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3207,13 +3231,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3221,22 +3249,22 @@
       <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3269,12 +3297,12 @@
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3323,12 +3351,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3364,7 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3346,7 +3374,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3384,12 +3412,12 @@
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3403,43 +3431,162 @@
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr">
         <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W26" s="2" t="inlineStr">
+      <c r="W27" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X26" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr">
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z26" s="2" t="inlineStr">
+      <c r="Z27" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
-      <c r="AC26" s="2" t="inlineStr">
-        <is>
-          <t>—/18</t>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东78路.xlsx
+++ b/data/export/2026-10-23-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1346,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1403,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1576,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -1609,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1633,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1697,24 +1713,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1724,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1773,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1806,32 +1822,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -1839,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1863,33 +1883,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1917,32 +1941,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -1950,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1974,33 +2002,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2028,32 +2060,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -2061,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2085,33 +2121,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2250,32 +2290,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2283,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2307,33 +2351,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2433,7 +2481,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2472,32 +2520,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2505,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2529,17 +2581,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2549,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2770,7 +2822,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2785,7 +2837,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2898,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2885,7 +2937,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2900,7 +2952,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2961,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3126,7 +3178,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3239,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3226,7 +3278,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3241,7 +3293,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3356,7 +3408,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3469,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3471,7 +3523,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3479,22 +3531,22 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3527,12 +3579,12 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3546,47 +3598,1193 @@
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W27" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z27" s="2" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr">
-        <is>
-          <t>6/18</t>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东78路.xlsx
+++ b/data/export/2026-10-23-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2750,32 +2750,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2783,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2807,17 +2811,17 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2827,17 +2831,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2865,32 +2869,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -2898,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2922,17 +2930,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2942,7 +2950,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -2952,7 +2960,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2980,32 +2988,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -3013,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3037,17 +3049,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3057,13 +3069,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3163,7 +3179,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3178,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3206,32 +3222,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3239,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3263,17 +3283,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3283,17 +3303,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3321,32 +3341,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -3354,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3378,17 +3402,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3398,17 +3422,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3436,32 +3460,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3469,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3493,32 +3521,32 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3584,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3623,7 +3651,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3638,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3666,32 +3694,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3699,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3723,37 +3755,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3781,32 +3813,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3814,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3838,17 +3874,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3858,17 +3894,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4044,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4083,7 +4119,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4098,7 +4134,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4213,7 +4249,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4310,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4328,7 +4364,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4389,7 +4425,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,7 +4536,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4544,17 +4580,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4651,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4659,7 +4695,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4669,7 +4705,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4677,22 +4713,22 @@
       <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4725,12 +4761,12 @@
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4779,12 +4815,587 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东78路.xlsx
+++ b/data/export/2026-10-23-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,13 +2486,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,22 +2830,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,17 +2949,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3079,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3194,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,22 +3302,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,7 +3540,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3551,7 +3555,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3666,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3785,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3823,24 +3827,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3850,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3899,12 +3903,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3932,32 +3936,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3965,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3989,37 +3997,37 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4047,32 +4055,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -4080,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4104,17 +4116,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4124,17 +4136,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4162,32 +4174,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4195,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4219,37 +4235,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4349,7 +4365,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4364,7 +4380,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4392,32 +4408,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4425,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4449,17 +4469,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4469,13 +4489,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4503,32 +4527,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4536,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4560,37 +4588,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4618,32 +4646,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4651,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4675,32 +4707,32 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4766,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4820,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4848,32 +4880,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4881,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4905,37 +4941,37 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4996,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5035,7 +5071,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5050,7 +5086,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5147,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5165,7 +5201,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5280,7 +5316,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5288,22 +5324,22 @@
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5341,7 +5377,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5355,47 +5391,852 @@
       <c r="T42" s="2" t="inlineStr"/>
       <c r="U42" s="2" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>11:10</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W42" s="2" t="inlineStr">
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z42" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
+      <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>102.0</t>
         </is>
       </c>
-      <c r="AC42" s="2" t="inlineStr">
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>95.3</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
         <is>
           <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东78路.xlsx
+++ b/data/export/2026-10-23-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,17 +2366,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3545,17 +3545,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,22 +3655,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,17 +4012,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,22 +4131,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,17 +4250,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4890,19 +4890,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4999,32 +4999,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5032,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5056,17 +5060,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5076,17 +5080,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5114,32 +5118,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5147,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5171,37 +5179,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5344,32 +5352,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5377,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5401,32 +5413,32 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5459,32 +5471,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5492,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5516,37 +5532,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5574,32 +5590,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5607,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5631,32 +5651,32 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5722,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5761,7 +5781,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5776,7 +5796,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5857,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5891,7 +5911,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6067,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6116,12 +6136,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6202,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6226,17 +6246,592 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>84.7</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB49" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="AC49" s="2" t="inlineStr">
-        <is>
-          <t>5/18</t>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>84.7</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>89.7</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东78路.xlsx
+++ b/data/export/2026-10-23-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,22 +2830,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3302,22 +3302,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3540,22 +3540,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4603,22 +4603,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4956,22 +4956,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5075,22 +5075,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5600,24 +5600,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5824,32 +5824,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5857,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5881,37 +5885,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5976,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6011,7 +6015,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6054,32 +6058,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6087,7 +6095,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6111,37 +6119,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6169,32 +6177,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6202,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6226,37 +6238,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6329,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6432,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6486,7 +6498,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6559,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6662,7 +6674,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6711,7 +6723,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6777,7 +6789,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6835,6 +6847,581 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>90.2</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-23-浦东78路.xlsx
+++ b/data/export/2026-10-23-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,22 +3655,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5194,22 +5194,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6187,24 +6187,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6296,32 +6296,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6329,7 +6333,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6353,37 +6357,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6448,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6483,7 +6487,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6526,32 +6530,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6559,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6583,17 +6591,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6603,12 +6611,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6674,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6789,7 +6797,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6904,7 +6912,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7019,7 +7027,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7073,7 +7081,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7142,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7183,12 +7191,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7257,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7364,7 +7372,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7413,12 +7421,242 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>89.7</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>84.7</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东78路.xlsx
+++ b/data/export/2026-10-23-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4370,17 +4370,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5786,17 +5786,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6649,32 +6649,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6682,7 +6686,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6706,17 +6710,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6726,12 +6730,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6764,32 +6768,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -6797,7 +6805,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6821,17 +6829,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6841,17 +6849,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6920,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7027,7 +7035,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7142,7 +7150,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7257,7 +7265,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7372,7 +7380,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7487,7 +7495,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7602,7 +7610,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7660,6 +7668,232 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-23-浦东78路.xlsx
+++ b/data/export/2026-10-23-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,14 +1660,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>94.5</t>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,22 +2830,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,14 +3893,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>94.5</t>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4603,22 +4603,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4727,17 +4727,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4765,12 +4765,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程39%处后消失；随后反向物理轨迹由seq25推进至seq33，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4806,10 +4806,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>五莲路荷泽路</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="S37" s="2" t="inlineStr"/>
-      <c r="T37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq17映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
@@ -4837,7 +4849,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4917,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4971,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5090,7 +5102,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5209,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5508,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5562,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5666,7 +5678,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5742,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5781,7 +5793,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5791,7 +5803,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5861,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5900,22 +5912,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6020,17 +6032,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6149,7 +6161,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6268,7 +6280,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6387,7 +6399,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6567,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6621,7 +6633,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6725,7 +6737,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6778,24 +6790,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6805,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6844,7 +6856,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6854,7 +6866,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6887,32 +6899,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6920,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6944,37 +6960,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7002,32 +7018,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7035,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7059,17 +7079,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7079,17 +7099,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7204,7 +7224,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7285,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7380,7 +7400,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7434,7 +7454,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7515,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7549,7 +7569,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7630,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,7 +7745,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7779,7 +7799,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7860,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7894,6 +7914,922 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>79.2</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-23-浦东78路.xlsx
+++ b/data/export/2026-10-23-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,18 +2251,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,7 +2370,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2442,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2561,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,17 +2604,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2676,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2791,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2845,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,7 +2953,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2964,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3198,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3302,7 +3306,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3317,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,22 +3425,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3540,22 +3544,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,22 +3659,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,7 +3778,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3789,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3908,7 +3912,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,22 +4016,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,17 +4135,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4211,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,7 +4254,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4326,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4380,7 +4384,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4564,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4618,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4722,7 +4726,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4737,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4774,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程39%处后消失；随后反向物理轨迹由seq25推进至seq33，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程39%处后消失；随后反向物理轨迹由seq25推进至seq37，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4798,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4864,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4968,7 +4972,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4983,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5087,22 +5091,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,22 +5210,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5321,7 +5325,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5336,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5440,22 +5444,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5559,17 +5563,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5639,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5678,7 +5682,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5754,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5808,7 +5812,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5927,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6027,7 +6031,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6042,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6146,7 +6150,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6161,7 +6165,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6265,22 +6269,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6345,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6384,22 +6388,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6499,22 +6503,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6618,17 +6622,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6698,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6737,7 +6741,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6817,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6871,7 +6875,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6990,7 +6994,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7094,7 +7098,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7109,7 +7113,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7209,7 +7213,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7224,7 +7228,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7252,32 +7256,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7285,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7309,32 +7317,32 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7367,32 +7375,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7400,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7424,37 +7436,37 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7482,32 +7494,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7515,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7539,37 +7555,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7597,32 +7613,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7630,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7654,37 +7674,37 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7712,32 +7732,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7745,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7769,32 +7793,32 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7827,32 +7851,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -7860,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7884,33 +7912,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB63" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7938,32 +7970,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7971,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7995,37 +8031,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8122,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8125,7 +8161,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8201,7 +8237,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8255,7 +8291,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8352,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8427,7 +8463,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8481,7 +8517,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8578,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8596,7 +8632,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8657,7 +8693,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8711,7 +8747,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8808,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8830,6 +8866,1271 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>90.2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>82.2</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>90.8</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>88.4</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>79.2</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-23-浦东78路.xlsx
+++ b/data/export/2026-10-23-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,17 +2136,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,22 +2485,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,18 +2719,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,22 +2838,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,22 +2957,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,22 +3191,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3321,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3440,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,7 +3548,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3620,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3674,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,22 +3782,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3897,22 +3901,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4031,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4150,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4330,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,17 +4373,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4449,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4488,22 +4492,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,22 +4611,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,22 +4730,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,22 +4857,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4987,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,7 +5095,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5171,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5225,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,22 +5329,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5459,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5578,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5758,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5797,17 +5801,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5877,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5916,22 +5920,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6031,22 +6035,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6165,7 +6169,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6269,7 +6273,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6349,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6403,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6518,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6637,7 +6641,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6821,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6860,17 +6864,17 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6940,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6979,22 +6983,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7098,22 +7102,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7228,7 +7232,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7347,7 +7351,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7451,7 +7455,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7531,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7585,7 +7589,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7704,7 +7708,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7823,7 +7827,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7942,7 +7946,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8061,7 +8065,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8204,32 +8208,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8237,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8261,37 +8269,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8319,32 +8327,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8352,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8376,33 +8388,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8430,32 +8446,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8463,7 +8483,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8487,32 +8507,32 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8545,32 +8565,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8578,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8602,37 +8626,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8660,32 +8684,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8693,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8717,37 +8745,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8775,32 +8803,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8808,7 +8840,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8832,37 +8864,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8890,32 +8922,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8923,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8947,37 +8983,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9005,32 +9041,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9038,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9062,37 +9102,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9207,7 +9247,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9307,7 +9347,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9383,7 +9423,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9437,7 +9477,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9538,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9552,7 +9592,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9613,7 +9653,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9667,7 +9707,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9728,7 +9768,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9782,7 +9822,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9843,7 +9883,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9897,7 +9937,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9958,7 +9998,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10012,7 +10052,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10113,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10131,6 +10171,1041 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>82.2</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-23-浦东78路.xlsx
+++ b/data/export/2026-10-23-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,22 +2251,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,22 +2604,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,22 +3310,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3553,17 +3553,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5219,17 +5219,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6154,22 +6154,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6278,17 +6278,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6397,17 +6397,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7217,22 +7217,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7336,22 +7336,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7460,17 +7460,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7579,17 +7579,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7931,22 +7931,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9051,24 +9051,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>107分钟</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9160,32 +9160,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9193,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9217,37 +9221,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9275,32 +9279,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9308,7 +9316,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9332,17 +9340,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9352,17 +9360,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9390,32 +9398,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9423,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9447,37 +9459,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9538,7 +9550,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9577,7 +9589,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9592,7 +9604,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9620,32 +9632,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9653,7 +9669,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9677,17 +9693,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9697,17 +9713,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9784,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9807,7 +9823,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9822,7 +9838,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9850,32 +9866,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -9883,7 +9903,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9907,37 +9927,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9998,7 +10018,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10037,7 +10057,7 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10052,7 +10072,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10113,7 +10133,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10228,7 +10248,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10282,7 +10302,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10363,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10382,7 +10402,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10458,7 +10478,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10512,7 +10532,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10573,7 +10593,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10612,7 +10632,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10627,7 +10647,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10688,7 +10708,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10742,7 +10762,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10803,7 +10823,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10857,7 +10877,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10918,7 +10938,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10972,7 +10992,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11033,7 +11053,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11077,17 +11097,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11148,7 +11168,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11197,12 +11217,932 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>96.4</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>94.8</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
           <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>88.4</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东78路.xlsx
+++ b/data/export/2026-10-23-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2375,17 +2375,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,22 +2485,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2962,17 +2962,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3434,17 +3434,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,22 +3782,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4263,17 +4263,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4492,22 +4492,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,22 +5329,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5691,17 +5691,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6040,17 +6040,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6750,17 +6750,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6988,17 +6988,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7107,17 +7107,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8055,17 +8055,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8170,17 +8170,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8879,22 +8879,22 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9003,17 +9003,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9117,22 +9117,22 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9985,32 +9985,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10018,7 +10022,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10042,17 +10046,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10062,17 +10066,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10100,32 +10104,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10133,7 +10141,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10157,17 +10165,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10177,17 +10185,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10256,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10287,7 +10295,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10302,7 +10310,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10371,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10478,7 +10486,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10532,7 +10540,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10593,7 +10601,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10647,7 +10655,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10675,32 +10683,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10708,7 +10720,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10732,37 +10744,37 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10790,32 +10802,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>111分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10823,7 +10839,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10847,17 +10863,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10867,17 +10883,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10905,32 +10921,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10938,7 +10958,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10962,17 +10982,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -10982,17 +11002,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11053,7 +11073,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11107,7 +11127,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -11135,32 +11155,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11168,7 +11192,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11192,37 +11216,37 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11307,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11337,7 +11361,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11398,7 +11422,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11452,7 +11476,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11494,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -11513,7 +11537,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11527,7 +11551,7 @@
       <c r="T94" s="2" t="inlineStr"/>
       <c r="U94" s="2" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="V94" s="2" t="inlineStr">
@@ -11552,7 +11576,7 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -11567,7 +11591,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11585,7 +11609,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -11628,7 +11652,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11642,7 +11666,7 @@
       <c r="T95" s="2" t="inlineStr"/>
       <c r="U95" s="2" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="V95" s="2" t="inlineStr">
@@ -11682,7 +11706,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11700,7 +11724,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -11743,7 +11767,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11757,7 +11781,7 @@
       <c r="T96" s="2" t="inlineStr"/>
       <c r="U96" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="V96" s="2" t="inlineStr">
@@ -11815,7 +11839,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -11858,7 +11882,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11872,7 +11896,7 @@
       <c r="T97" s="2" t="inlineStr"/>
       <c r="U97" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="V97" s="2" t="inlineStr">
@@ -11930,7 +11954,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -11973,7 +11997,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -11987,7 +12011,7 @@
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="V98" s="2" t="inlineStr">
@@ -12017,17 +12041,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -12088,7 +12112,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12142,7 +12166,467 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
           <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>97.2</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>99.7</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>94.8</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东78路.xlsx
+++ b/data/export/2026-10-23-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AC105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>96.4</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3315,17 +3315,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>96.4</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,22 +3429,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3553,17 +3553,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4025,17 +4025,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4144,17 +4144,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>96.4</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5453,17 +5453,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5572,17 +5572,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6159,17 +6159,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>96.4</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6278,17 +6278,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6512,17 +6512,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6631,17 +6631,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7222,17 +7222,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>96.4</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7460,17 +7460,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7698,17 +7698,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7817,17 +7817,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8050,22 +8050,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8408,17 +8408,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -9013,7 +9013,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9241,17 +9241,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>96.4</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9360,17 +9360,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9594,17 +9594,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9828,17 +9828,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10061,22 +10061,22 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10195,7 +10195,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10415,17 +10415,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10601,7 +10601,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -11012,7 +11012,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11040,32 +11040,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11073,7 +11077,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11097,17 +11101,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11117,17 +11121,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11165,24 +11169,24 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -11192,7 +11196,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11241,12 +11245,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11274,32 +11278,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11307,7 +11315,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11331,17 +11339,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11351,17 +11359,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>96.4</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -11389,32 +11397,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11422,7 +11434,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11446,17 +11458,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11466,17 +11478,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11549,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11591,7 +11603,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11619,32 +11631,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -11652,7 +11668,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11676,17 +11692,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11696,7 +11712,7 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
@@ -11706,7 +11722,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11734,32 +11750,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11767,7 +11787,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11791,17 +11811,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11811,17 +11831,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -11849,32 +11869,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11882,7 +11906,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11906,17 +11930,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11926,17 +11950,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11964,32 +11988,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -11997,7 +12025,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12021,37 +12049,37 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA98" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -12112,7 +12140,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12227,7 +12255,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12266,7 +12294,7 @@
       </c>
       <c r="Z100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA100" s="2" t="inlineStr">
@@ -12281,7 +12309,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -12342,7 +12370,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12391,12 +12419,12 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -12457,7 +12485,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12511,7 +12539,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12600,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12626,7 +12654,237 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>93.2</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-浦东78路.xlsx
+++ b/data/export/2026-10-23-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC105"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,17 +2485,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3196,17 +3196,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3434,17 +3434,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,17 +3906,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4492,17 +4492,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4862,17 +4862,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5334,17 +5334,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7341,17 +7341,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8055,17 +8055,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8289,17 +8289,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8646,17 +8646,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8879,17 +8879,17 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9122,17 +9122,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9479,17 +9479,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10066,17 +10066,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10300,17 +10300,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10601,7 +10601,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10645,17 +10645,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10759,17 +10759,17 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11196,7 +11196,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11240,17 +11240,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11593,17 +11593,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11879,24 +11879,24 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11998,24 +11998,24 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12069,17 +12069,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12107,32 +12107,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -12140,7 +12144,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12164,17 +12168,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12184,17 +12188,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -12222,32 +12226,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12255,7 +12263,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12279,17 +12287,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12299,17 +12307,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -12337,32 +12345,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12370,7 +12382,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12394,17 +12406,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12414,17 +12426,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -12452,32 +12464,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:27</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12485,7 +12501,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12509,32 +12525,32 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
@@ -12567,32 +12583,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12600,7 +12620,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12624,17 +12644,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12644,17 +12664,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -12682,32 +12702,36 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -12715,7 +12739,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12739,17 +12763,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12759,17 +12783,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12854,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12874,17 +12898,132 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
         </is>
       </c>
     </row>
